--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710"/>
+    <workbookView windowWidth="18350" windowHeight="8710" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet8" sheetId="8" r:id="rId2"/>
     <sheet name="Sheet9" sheetId="9" r:id="rId3"/>
+    <sheet name="ROR_has_no_regulation_cap" sheetId="10" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -127,8 +128,40 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>xli9</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">
+dam hydropower should also have some limits, bcz not all dam hydropower are TGR</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="33">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -194,6 +227,39 @@
   </si>
   <si>
     <t>DELIV</t>
+  </si>
+  <si>
+    <t>*COM_FR is worse than utilization rate for ROR, but we need to put this constraint to avoild regulation capacities</t>
+  </si>
+  <si>
+    <t>~TFM_INS</t>
+  </si>
+  <si>
+    <t>attribute</t>
+  </si>
+  <si>
+    <t>PSET_SET</t>
+  </si>
+  <si>
+    <t>PSET_CI</t>
+  </si>
+  <si>
+    <t>pset_pn</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>ELE</t>
+  </si>
+  <si>
+    <t>ELCHYD</t>
+  </si>
+  <si>
+    <t>*HYD-DAM*</t>
+  </si>
+  <si>
+    <t>*HYD-ROR*</t>
   </si>
 </sst>
 </file>
@@ -206,13 +272,19 @@
     <numFmt numFmtId="176" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.2"/>
+      <color rgb="FF212529"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -370,9 +442,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -380,13 +454,24 @@
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -688,7 +773,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
@@ -705,55 +790,52 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -768,80 +850,86 @@
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="51">
+  <cellStyles count="52">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -893,6 +981,7 @@
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
     <cellStyle name="Normal 10" xfId="49"/>
     <cellStyle name="Normale_Scen_UC_IND-StrucConst" xfId="50"/>
+    <cellStyle name="Input 2" xfId="51"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1371,7 +1460,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="3">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -1406,4 +1495,94 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A3:K11"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="25.0909090909091" customWidth="1"/>
+    <col min="2" max="2" width="28.7272727272727" customWidth="1"/>
+    <col min="5" max="5" width="12.8181818181818" customWidth="1"/>
+    <col min="7" max="7" width="13.2727272727273" customWidth="1"/>
+    <col min="9" max="9" width="12.4545454545455" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:11">
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" ht="16" spans="1:11">
+      <c r="A4" s="1"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10">
+        <v>0.48</v>
+      </c>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="K11" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710" activeTab="3"/>
+    <workbookView windowWidth="18350" windowHeight="8710" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet8" sheetId="8" r:id="rId2"/>
     <sheet name="Sheet9" sheetId="9" r:id="rId3"/>
     <sheet name="ROR_has_no_regulation_cap" sheetId="10" r:id="rId4"/>
+    <sheet name="Ramp_rate_constraints" sheetId="11" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -160,8 +161,40 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Xiao Li</author>
+  </authors>
+  <commentList>
+    <comment ref="C77" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <charset val="0"/>
+          </rPr>
+          <t>Xiao Li:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">
+we consider no new hydro-investment for AB and SK due to limited potential</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="54">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -260,6 +293,69 @@
   </si>
   <si>
     <t>*HYD-ROR*</t>
+  </si>
+  <si>
+    <t>TechName</t>
+  </si>
+  <si>
+    <t>ACT_CSTRMP</t>
+  </si>
+  <si>
+    <t>ACT_UPS~UP</t>
+  </si>
+  <si>
+    <t>*bio*</t>
+  </si>
+  <si>
+    <t>*coa*, *lig*</t>
+  </si>
+  <si>
+    <t>EA_OIL*, EP_OIL*</t>
+  </si>
+  <si>
+    <t>en_gas*, ea_gas*, ep_gas*</t>
+  </si>
+  <si>
+    <t>*HPS*</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt*</t>
+  </si>
+  <si>
+    <t>Util_Rep_Batt*</t>
+  </si>
+  <si>
+    <t>*nuc*</t>
+  </si>
+  <si>
+    <t>~TFM_AVA</t>
+  </si>
+  <si>
+    <t>PSET_PN</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>AT</t>
+  </si>
+  <si>
+    <t>BC</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>QU</t>
+  </si>
+  <si>
+    <t>ENCAN01_SMR</t>
   </si>
 </sst>
 </file>
@@ -272,7 +368,7 @@
     <numFmt numFmtId="176" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -281,10 +377,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <sz val="10.2"/>
       <color rgb="FF212529"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="0"/>
     </font>
     <font>
       <u/>
@@ -431,11 +544,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
@@ -455,8 +563,19 @@
       <charset val="0"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
       <charset val="0"/>
     </font>
   </fonts>
@@ -773,7 +892,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="52">
+  <cellStyleXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
@@ -790,146 +909,158 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="52">
+  <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -982,6 +1113,7 @@
     <cellStyle name="Normal 10" xfId="49"/>
     <cellStyle name="Normale_Scen_UC_IND-StrucConst" xfId="50"/>
     <cellStyle name="Input 2" xfId="51"/>
+    <cellStyle name="Normal 2" xfId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1460,7 +1592,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="14">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -1516,7 +1648,7 @@
       </c>
     </row>
     <row r="4" ht="16" spans="1:11">
-      <c r="A4" s="1"/>
+      <c r="A4" s="12"/>
     </row>
     <row r="7" spans="1:11">
       <c r="D7" t="s">
@@ -1573,12 +1705,620 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="I10"/>
-      <c r="J10"/>
-      <c r="K10" s="2"/>
+      <c r="K10" s="13"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="2"/>
+      <c r="K11" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C5:K85"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="3" max="3" width="24.1818181818182" customWidth="1"/>
+    <col min="4" max="4" width="14.0909090909091" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="3:6">
+      <c r="C5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="3:6">
+      <c r="C6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="3:6">
+      <c r="C7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="6">
+        <v>10</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="3:6">
+      <c r="C8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="6">
+        <v>7</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" ht="16" spans="3:6">
+      <c r="C9" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="6">
+        <v>10</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="3:6">
+      <c r="C10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="6">
+        <v>8</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" ht="16" spans="3:6">
+      <c r="C11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" ht="16" spans="3:6">
+      <c r="C12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="3:6">
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="3:6">
+      <c r="C14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" ht="16" spans="3:6">
+      <c r="C15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="3:6">
+      <c r="C16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="2">
+        <v>35</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="3:6">
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="3:6">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="3:6">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="3:6">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="3:6">
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" spans="3:6">
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="3:6">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" spans="3:6">
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" spans="3:6">
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="3:6">
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" spans="3:6">
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" spans="3:6">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+    </row>
+    <row r="29" spans="3:6">
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+    </row>
+    <row r="30" spans="3:6">
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+    </row>
+    <row r="31" spans="3:6">
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+    </row>
+    <row r="32" spans="3:6">
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+    </row>
+    <row r="38" spans="3:5">
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+    </row>
+    <row r="54" spans="3:11">
+      <c r="C54" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="56" spans="3:11">
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+    </row>
+    <row r="57" spans="3:11">
+      <c r="C57" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="58" spans="3:11">
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="11"/>
+      <c r="K58" s="11"/>
+    </row>
+    <row r="59" spans="3:11">
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="11"/>
+      <c r="K59" s="11"/>
+    </row>
+    <row r="60" spans="3:11">
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="11"/>
+      <c r="K60" s="11"/>
+    </row>
+    <row r="61" spans="3:11">
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="11"/>
+      <c r="K61" s="11"/>
+    </row>
+    <row r="62" spans="3:11">
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="11"/>
+      <c r="J62" s="11"/>
+      <c r="K62" s="11"/>
+    </row>
+    <row r="63" spans="3:11">
+      <c r="C63" s="11"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="11"/>
+      <c r="I63" s="11"/>
+      <c r="J63" s="11"/>
+      <c r="K63" s="11"/>
+    </row>
+    <row r="64" spans="3:11">
+      <c r="C64" s="11"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="11"/>
+      <c r="J64" s="11"/>
+      <c r="K64" s="11"/>
+    </row>
+    <row r="65" spans="3:11">
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="11"/>
+      <c r="K65" s="11"/>
+    </row>
+    <row r="66" spans="3:11">
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="11"/>
+      <c r="K66" s="11"/>
+    </row>
+    <row r="67" spans="3:11">
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="11"/>
+      <c r="J67" s="11"/>
+      <c r="K67" s="11"/>
+    </row>
+    <row r="68" spans="3:11">
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="11"/>
+      <c r="I68" s="11"/>
+      <c r="J68" s="11"/>
+      <c r="K68" s="11"/>
+    </row>
+    <row r="69" spans="3:11">
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
+      <c r="K69" s="11"/>
+    </row>
+    <row r="70" spans="3:11">
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="11"/>
+      <c r="I70" s="11"/>
+      <c r="J70" s="11"/>
+      <c r="K70" s="11"/>
+    </row>
+    <row r="71" spans="3:11">
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
+      <c r="K71" s="11"/>
+    </row>
+    <row r="72" spans="3:11">
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="11"/>
+      <c r="K72" s="11"/>
+    </row>
+    <row r="73" spans="3:11">
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="11"/>
+      <c r="K73" s="11"/>
+    </row>
+    <row r="74" spans="3:11">
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11"/>
+      <c r="I74" s="11"/>
+      <c r="J74" s="11"/>
+      <c r="K74" s="11"/>
+    </row>
+    <row r="75" spans="3:11">
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="11"/>
+      <c r="J75" s="11"/>
+      <c r="K75" s="11"/>
+    </row>
+    <row r="76" spans="3:11">
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="11"/>
+      <c r="K76" s="11"/>
+    </row>
+    <row r="77" spans="3:11">
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="11"/>
+      <c r="J77" s="11"/>
+      <c r="K77" s="11"/>
+    </row>
+    <row r="78" spans="3:11">
+      <c r="C78" s="11"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="11"/>
+      <c r="J78" s="11"/>
+      <c r="K78" s="11"/>
+    </row>
+    <row r="79" spans="3:11">
+      <c r="C79" s="11"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="11"/>
+      <c r="G79" s="11"/>
+      <c r="H79" s="11"/>
+      <c r="I79" s="11"/>
+      <c r="J79" s="11"/>
+      <c r="K79" s="11"/>
+    </row>
+    <row r="80" spans="3:11">
+      <c r="C80" s="11"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="11"/>
+      <c r="J80" s="11"/>
+      <c r="K80" s="11"/>
+    </row>
+    <row r="81" spans="3:11">
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="11"/>
+      <c r="H81" s="11"/>
+      <c r="I81" s="11"/>
+      <c r="J81" s="11"/>
+      <c r="K81" s="11"/>
+    </row>
+    <row r="82" spans="3:11">
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
+      <c r="F82" s="11"/>
+      <c r="G82" s="11"/>
+      <c r="H82" s="11"/>
+      <c r="I82" s="11"/>
+      <c r="J82" s="11"/>
+      <c r="K82" s="11"/>
+    </row>
+    <row r="83" spans="3:11">
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11"/>
+      <c r="G83" s="11"/>
+      <c r="H83" s="11"/>
+      <c r="I83" s="11"/>
+      <c r="J83" s="11"/>
+      <c r="K83" s="11"/>
+    </row>
+    <row r="84" spans="3:11">
+      <c r="C84" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D84" s="11">
+        <v>1</v>
+      </c>
+      <c r="E84" s="11"/>
+      <c r="F84" s="11"/>
+      <c r="G84" s="11"/>
+      <c r="H84" s="11"/>
+      <c r="I84" s="11"/>
+      <c r="J84" s="11"/>
+      <c r="K84" s="11"/>
+    </row>
+    <row r="85" spans="3:11">
+      <c r="C85" s="11"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="11"/>
+      <c r="F85" s="11"/>
+      <c r="G85" s="11"/>
+      <c r="H85" s="11"/>
+      <c r="I85" s="11"/>
+      <c r="J85" s="11"/>
+      <c r="K85" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710" activeTab="4"/>
+    <workbookView windowWidth="18350" windowHeight="8710" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -194,7 +194,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="53">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -295,13 +295,10 @@
     <t>*HYD-ROR*</t>
   </si>
   <si>
-    <t>TechName</t>
-  </si>
-  <si>
     <t>ACT_CSTRMP</t>
   </si>
   <si>
-    <t>ACT_UPS~UP</t>
+    <t>ACT_UPS</t>
   </si>
   <si>
     <t>*bio*</t>
@@ -396,7 +393,6 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
     </font>
     <font>
@@ -563,17 +559,17 @@
       <charset val="0"/>
     </font>
     <font>
-      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -1043,20 +1039,17 @@
     <xf numFmtId="0" fontId="25" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -1592,7 +1585,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="11">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -1637,6 +1630,7 @@
   <cols>
     <col min="1" max="1" width="25.0909090909091" customWidth="1"/>
     <col min="2" max="2" width="28.7272727272727" customWidth="1"/>
+    <col min="4" max="4" width="105.363636363636" customWidth="1"/>
     <col min="5" max="5" width="12.8181818181818" customWidth="1"/>
     <col min="7" max="7" width="13.2727272727273" customWidth="1"/>
     <col min="9" max="9" width="12.4545454545455" customWidth="1"/>
@@ -1648,7 +1642,7 @@
       </c>
     </row>
     <row r="4" ht="16" spans="1:11">
-      <c r="A4" s="12"/>
+      <c r="A4" s="6"/>
     </row>
     <row r="7" spans="1:11">
       <c r="D7" t="s">
@@ -1705,10 +1699,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="13"/>
+      <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="13"/>
+      <c r="K11" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1736,67 +1730,67 @@
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="3:6">
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="3:6">
+      <c r="C7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="3:6">
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5">
+        <v>10</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="3:6">
+      <c r="C8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D8" s="5">
+        <v>7</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" ht="16" spans="3:6">
+      <c r="C9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="5">
         <v>10</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E9" s="5">
         <v>0</v>
       </c>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="3:6">
-      <c r="C8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="6">
-        <v>7</v>
-      </c>
-      <c r="E8" s="6">
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="3:6">
+      <c r="C10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="5">
+        <v>8</v>
+      </c>
+      <c r="E10" s="5">
         <v>0</v>
       </c>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" ht="16" spans="3:6">
-      <c r="C9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="6">
-        <v>10</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="3:6">
-      <c r="C10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="6">
-        <v>8</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0</v>
-      </c>
       <c r="F10" s="3"/>
     </row>
     <row r="11" ht="16" spans="3:6">
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="2">
@@ -1806,18 +1800,18 @@
       <c r="F11" s="3"/>
     </row>
     <row r="12" ht="16" spans="3:6">
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="2">
         <v>1.5</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="2"/>
       <c r="F12" s="3"/>
     </row>
     <row r="13" spans="3:6">
       <c r="C13" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D13" s="3">
         <v>2</v>
@@ -1829,7 +1823,7 @@
     </row>
     <row r="14" spans="3:6">
       <c r="C14" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
@@ -1840,8 +1834,8 @@
       <c r="F14" s="3"/>
     </row>
     <row r="15" ht="16" spans="3:6">
-      <c r="C15" s="9" t="s">
-        <v>42</v>
+      <c r="C15" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="D15" s="3">
         <v>0</v>
@@ -1853,7 +1847,7 @@
     </row>
     <row r="16" spans="3:6">
       <c r="C16" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" s="2">
         <v>35</v>
@@ -1888,45 +1882,45 @@
       <c r="F20" s="3"/>
     </row>
     <row r="21" spans="3:6">
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
       <c r="F21" s="3"/>
     </row>
     <row r="22" spans="3:6">
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
       <c r="F22" s="3"/>
     </row>
     <row r="23" spans="3:6">
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
       <c r="F23" s="3"/>
     </row>
     <row r="24" spans="3:6">
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
       <c r="F24" s="3"/>
     </row>
     <row r="25" spans="3:6">
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
       <c r="F25" s="3"/>
     </row>
     <row r="26" spans="3:6">
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
       <c r="F26" s="3"/>
     </row>
     <row r="27" spans="3:6">
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
       <c r="F27" s="3"/>
     </row>
     <row r="28" spans="3:6">
@@ -1960,365 +1954,365 @@
       <c r="F32" s="3"/>
     </row>
     <row r="38" spans="3:5">
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56" spans="3:11">
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
+      <c r="K56" s="9"/>
+    </row>
+    <row r="57" spans="3:11">
+      <c r="C57" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="56" spans="3:11">
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11"/>
-      <c r="I56" s="11"/>
-      <c r="J56" s="11"/>
-      <c r="K56" s="11"/>
-    </row>
-    <row r="57" spans="3:11">
-      <c r="C57" s="11" t="s">
+      <c r="D57" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D57" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E57" s="11" t="s">
+      <c r="F57" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="G57" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G57" s="11" t="s">
+      <c r="H57" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="H57" s="11" t="s">
+      <c r="I57" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="I57" s="11" t="s">
+      <c r="J57" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="J57" s="11" t="s">
+      <c r="K57" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="K57" s="11" t="s">
+    </row>
+    <row r="58" spans="3:11">
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
+      <c r="K58" s="9"/>
+    </row>
+    <row r="59" spans="3:11">
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="9"/>
+      <c r="K59" s="9"/>
+    </row>
+    <row r="60" spans="3:11">
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
+      <c r="I60" s="9"/>
+      <c r="J60" s="9"/>
+      <c r="K60" s="9"/>
+    </row>
+    <row r="61" spans="3:11">
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9"/>
+      <c r="I61" s="9"/>
+      <c r="J61" s="9"/>
+      <c r="K61" s="9"/>
+    </row>
+    <row r="62" spans="3:11">
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="9"/>
+      <c r="H62" s="9"/>
+      <c r="I62" s="9"/>
+      <c r="J62" s="9"/>
+      <c r="K62" s="9"/>
+    </row>
+    <row r="63" spans="3:11">
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="9"/>
+      <c r="F63" s="9"/>
+      <c r="G63" s="9"/>
+      <c r="H63" s="9"/>
+      <c r="I63" s="9"/>
+      <c r="J63" s="9"/>
+      <c r="K63" s="9"/>
+    </row>
+    <row r="64" spans="3:11">
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9"/>
+      <c r="I64" s="9"/>
+      <c r="J64" s="9"/>
+      <c r="K64" s="9"/>
+    </row>
+    <row r="65" spans="3:11">
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="9"/>
+      <c r="K65" s="9"/>
+    </row>
+    <row r="66" spans="3:11">
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="9"/>
+      <c r="I66" s="9"/>
+      <c r="J66" s="9"/>
+      <c r="K66" s="9"/>
+    </row>
+    <row r="67" spans="3:11">
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="9"/>
+      <c r="F67" s="9"/>
+      <c r="G67" s="9"/>
+      <c r="H67" s="9"/>
+      <c r="I67" s="9"/>
+      <c r="J67" s="9"/>
+      <c r="K67" s="9"/>
+    </row>
+    <row r="68" spans="3:11">
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="9"/>
+      <c r="I68" s="9"/>
+      <c r="J68" s="9"/>
+      <c r="K68" s="9"/>
+    </row>
+    <row r="69" spans="3:11">
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="9"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="9"/>
+      <c r="H69" s="9"/>
+      <c r="I69" s="9"/>
+      <c r="J69" s="9"/>
+      <c r="K69" s="9"/>
+    </row>
+    <row r="70" spans="3:11">
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="9"/>
+      <c r="H70" s="9"/>
+      <c r="I70" s="9"/>
+      <c r="J70" s="9"/>
+      <c r="K70" s="9"/>
+    </row>
+    <row r="71" spans="3:11">
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="9"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="9"/>
+      <c r="H71" s="9"/>
+      <c r="I71" s="9"/>
+      <c r="J71" s="9"/>
+      <c r="K71" s="9"/>
+    </row>
+    <row r="72" spans="3:11">
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="9"/>
+      <c r="F72" s="9"/>
+      <c r="G72" s="9"/>
+      <c r="H72" s="9"/>
+      <c r="I72" s="9"/>
+      <c r="J72" s="9"/>
+      <c r="K72" s="9"/>
+    </row>
+    <row r="73" spans="3:11">
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="9"/>
+      <c r="F73" s="9"/>
+      <c r="G73" s="9"/>
+      <c r="H73" s="9"/>
+      <c r="I73" s="9"/>
+      <c r="J73" s="9"/>
+      <c r="K73" s="9"/>
+    </row>
+    <row r="74" spans="3:11">
+      <c r="C74" s="9"/>
+      <c r="D74" s="9"/>
+      <c r="E74" s="9"/>
+      <c r="F74" s="9"/>
+      <c r="G74" s="9"/>
+      <c r="H74" s="9"/>
+      <c r="I74" s="9"/>
+      <c r="J74" s="9"/>
+      <c r="K74" s="9"/>
+    </row>
+    <row r="75" spans="3:11">
+      <c r="C75" s="9"/>
+      <c r="D75" s="9"/>
+      <c r="E75" s="9"/>
+      <c r="F75" s="9"/>
+      <c r="G75" s="9"/>
+      <c r="H75" s="9"/>
+      <c r="I75" s="9"/>
+      <c r="J75" s="9"/>
+      <c r="K75" s="9"/>
+    </row>
+    <row r="76" spans="3:11">
+      <c r="C76" s="9"/>
+      <c r="D76" s="9"/>
+      <c r="E76" s="9"/>
+      <c r="F76" s="9"/>
+      <c r="G76" s="9"/>
+      <c r="H76" s="9"/>
+      <c r="I76" s="9"/>
+      <c r="J76" s="9"/>
+      <c r="K76" s="9"/>
+    </row>
+    <row r="77" spans="3:11">
+      <c r="C77" s="9"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
+      <c r="K77" s="9"/>
+    </row>
+    <row r="78" spans="3:11">
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="9"/>
+      <c r="H78" s="9"/>
+      <c r="I78" s="9"/>
+      <c r="J78" s="9"/>
+      <c r="K78" s="9"/>
+    </row>
+    <row r="79" spans="3:11">
+      <c r="C79" s="9"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
+      <c r="G79" s="9"/>
+      <c r="H79" s="9"/>
+      <c r="I79" s="9"/>
+      <c r="J79" s="9"/>
+      <c r="K79" s="9"/>
+    </row>
+    <row r="80" spans="3:11">
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
+      <c r="G80" s="9"/>
+      <c r="H80" s="9"/>
+      <c r="I80" s="9"/>
+      <c r="J80" s="9"/>
+      <c r="K80" s="9"/>
+    </row>
+    <row r="81" spans="3:11">
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="9"/>
+      <c r="G81" s="9"/>
+      <c r="H81" s="9"/>
+      <c r="I81" s="9"/>
+      <c r="J81" s="9"/>
+      <c r="K81" s="9"/>
+    </row>
+    <row r="82" spans="3:11">
+      <c r="C82" s="9"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="9"/>
+      <c r="F82" s="9"/>
+      <c r="G82" s="9"/>
+      <c r="H82" s="9"/>
+      <c r="I82" s="9"/>
+      <c r="J82" s="9"/>
+      <c r="K82" s="9"/>
+    </row>
+    <row r="83" spans="3:11">
+      <c r="C83" s="9"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="9"/>
+      <c r="F83" s="9"/>
+      <c r="G83" s="9"/>
+      <c r="H83" s="9"/>
+      <c r="I83" s="9"/>
+      <c r="J83" s="9"/>
+      <c r="K83" s="9"/>
+    </row>
+    <row r="84" spans="3:11">
+      <c r="C84" s="9" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="58" spans="3:11">
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="11"/>
-      <c r="I58" s="11"/>
-      <c r="J58" s="11"/>
-      <c r="K58" s="11"/>
-    </row>
-    <row r="59" spans="3:11">
-      <c r="C59" s="11"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="11"/>
-      <c r="I59" s="11"/>
-      <c r="J59" s="11"/>
-      <c r="K59" s="11"/>
-    </row>
-    <row r="60" spans="3:11">
-      <c r="C60" s="11"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
-      <c r="H60" s="11"/>
-      <c r="I60" s="11"/>
-      <c r="J60" s="11"/>
-      <c r="K60" s="11"/>
-    </row>
-    <row r="61" spans="3:11">
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="11"/>
-      <c r="I61" s="11"/>
-      <c r="J61" s="11"/>
-      <c r="K61" s="11"/>
-    </row>
-    <row r="62" spans="3:11">
-      <c r="C62" s="11"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="11"/>
-      <c r="I62" s="11"/>
-      <c r="J62" s="11"/>
-      <c r="K62" s="11"/>
-    </row>
-    <row r="63" spans="3:11">
-      <c r="C63" s="11"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
-      <c r="H63" s="11"/>
-      <c r="I63" s="11"/>
-      <c r="J63" s="11"/>
-      <c r="K63" s="11"/>
-    </row>
-    <row r="64" spans="3:11">
-      <c r="C64" s="11"/>
-      <c r="D64" s="11"/>
-      <c r="E64" s="11"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="11"/>
-      <c r="H64" s="11"/>
-      <c r="I64" s="11"/>
-      <c r="J64" s="11"/>
-      <c r="K64" s="11"/>
-    </row>
-    <row r="65" spans="3:11">
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
-      <c r="H65" s="11"/>
-      <c r="I65" s="11"/>
-      <c r="J65" s="11"/>
-      <c r="K65" s="11"/>
-    </row>
-    <row r="66" spans="3:11">
-      <c r="C66" s="11"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="11"/>
-      <c r="H66" s="11"/>
-      <c r="I66" s="11"/>
-      <c r="J66" s="11"/>
-      <c r="K66" s="11"/>
-    </row>
-    <row r="67" spans="3:11">
-      <c r="C67" s="11"/>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="11"/>
-      <c r="I67" s="11"/>
-      <c r="J67" s="11"/>
-      <c r="K67" s="11"/>
-    </row>
-    <row r="68" spans="3:11">
-      <c r="C68" s="11"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="11"/>
-      <c r="I68" s="11"/>
-      <c r="J68" s="11"/>
-      <c r="K68" s="11"/>
-    </row>
-    <row r="69" spans="3:11">
-      <c r="C69" s="11"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="11"/>
-      <c r="H69" s="11"/>
-      <c r="I69" s="11"/>
-      <c r="J69" s="11"/>
-      <c r="K69" s="11"/>
-    </row>
-    <row r="70" spans="3:11">
-      <c r="C70" s="11"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="11"/>
-      <c r="G70" s="11"/>
-      <c r="H70" s="11"/>
-      <c r="I70" s="11"/>
-      <c r="J70" s="11"/>
-      <c r="K70" s="11"/>
-    </row>
-    <row r="71" spans="3:11">
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="11"/>
-      <c r="H71" s="11"/>
-      <c r="I71" s="11"/>
-      <c r="J71" s="11"/>
-      <c r="K71" s="11"/>
-    </row>
-    <row r="72" spans="3:11">
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="11"/>
-      <c r="I72" s="11"/>
-      <c r="J72" s="11"/>
-      <c r="K72" s="11"/>
-    </row>
-    <row r="73" spans="3:11">
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="11"/>
-      <c r="I73" s="11"/>
-      <c r="J73" s="11"/>
-      <c r="K73" s="11"/>
-    </row>
-    <row r="74" spans="3:11">
-      <c r="C74" s="11"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="11"/>
-      <c r="H74" s="11"/>
-      <c r="I74" s="11"/>
-      <c r="J74" s="11"/>
-      <c r="K74" s="11"/>
-    </row>
-    <row r="75" spans="3:11">
-      <c r="C75" s="11"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="11"/>
-      <c r="H75" s="11"/>
-      <c r="I75" s="11"/>
-      <c r="J75" s="11"/>
-      <c r="K75" s="11"/>
-    </row>
-    <row r="76" spans="3:11">
-      <c r="C76" s="11"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="11"/>
-      <c r="H76" s="11"/>
-      <c r="I76" s="11"/>
-      <c r="J76" s="11"/>
-      <c r="K76" s="11"/>
-    </row>
-    <row r="77" spans="3:11">
-      <c r="C77" s="11"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="11"/>
-      <c r="H77" s="11"/>
-      <c r="I77" s="11"/>
-      <c r="J77" s="11"/>
-      <c r="K77" s="11"/>
-    </row>
-    <row r="78" spans="3:11">
-      <c r="C78" s="11"/>
-      <c r="D78" s="11"/>
-      <c r="E78" s="11"/>
-      <c r="F78" s="11"/>
-      <c r="G78" s="11"/>
-      <c r="H78" s="11"/>
-      <c r="I78" s="11"/>
-      <c r="J78" s="11"/>
-      <c r="K78" s="11"/>
-    </row>
-    <row r="79" spans="3:11">
-      <c r="C79" s="11"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="11"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="11"/>
-      <c r="H79" s="11"/>
-      <c r="I79" s="11"/>
-      <c r="J79" s="11"/>
-      <c r="K79" s="11"/>
-    </row>
-    <row r="80" spans="3:11">
-      <c r="C80" s="11"/>
-      <c r="D80" s="11"/>
-      <c r="E80" s="11"/>
-      <c r="F80" s="11"/>
-      <c r="G80" s="11"/>
-      <c r="H80" s="11"/>
-      <c r="I80" s="11"/>
-      <c r="J80" s="11"/>
-      <c r="K80" s="11"/>
-    </row>
-    <row r="81" spans="3:11">
-      <c r="C81" s="11"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
-      <c r="G81" s="11"/>
-      <c r="H81" s="11"/>
-      <c r="I81" s="11"/>
-      <c r="J81" s="11"/>
-      <c r="K81" s="11"/>
-    </row>
-    <row r="82" spans="3:11">
-      <c r="C82" s="11"/>
-      <c r="D82" s="11"/>
-      <c r="E82" s="11"/>
-      <c r="F82" s="11"/>
-      <c r="G82" s="11"/>
-      <c r="H82" s="11"/>
-      <c r="I82" s="11"/>
-      <c r="J82" s="11"/>
-      <c r="K82" s="11"/>
-    </row>
-    <row r="83" spans="3:11">
-      <c r="C83" s="11"/>
-      <c r="D83" s="11"/>
-      <c r="E83" s="11"/>
-      <c r="F83" s="11"/>
-      <c r="G83" s="11"/>
-      <c r="H83" s="11"/>
-      <c r="I83" s="11"/>
-      <c r="J83" s="11"/>
-      <c r="K83" s="11"/>
-    </row>
-    <row r="84" spans="3:11">
-      <c r="C84" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D84" s="11">
+      <c r="D84" s="9">
         <v>1</v>
       </c>
-      <c r="E84" s="11"/>
-      <c r="F84" s="11"/>
-      <c r="G84" s="11"/>
-      <c r="H84" s="11"/>
-      <c r="I84" s="11"/>
-      <c r="J84" s="11"/>
-      <c r="K84" s="11"/>
+      <c r="E84" s="9"/>
+      <c r="F84" s="9"/>
+      <c r="G84" s="9"/>
+      <c r="H84" s="9"/>
+      <c r="I84" s="9"/>
+      <c r="J84" s="9"/>
+      <c r="K84" s="9"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="11"/>
-      <c r="D85" s="11"/>
-      <c r="E85" s="11"/>
-      <c r="F85" s="11"/>
-      <c r="G85" s="11"/>
-      <c r="H85" s="11"/>
-      <c r="I85" s="11"/>
-      <c r="J85" s="11"/>
-      <c r="K85" s="11"/>
+      <c r="C85" s="9"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="9"/>
+      <c r="F85" s="9"/>
+      <c r="G85" s="9"/>
+      <c r="H85" s="9"/>
+      <c r="I85" s="9"/>
+      <c r="J85" s="9"/>
+      <c r="K85" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710" activeTab="3"/>
+    <workbookView windowWidth="18350" windowHeight="8710" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -194,7 +194,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="54">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -295,34 +295,37 @@
     <t>*HYD-ROR*</t>
   </si>
   <si>
+    <t>PSET_CO</t>
+  </si>
+  <si>
+    <t>*bio*</t>
+  </si>
+  <si>
     <t>ACT_CSTRMP</t>
   </si>
   <si>
+    <t>*coa*, *lig*</t>
+  </si>
+  <si>
+    <t>EA_OIL*, EP_OIL*</t>
+  </si>
+  <si>
+    <t>en_gas*, ea_gas*, ep_gas*</t>
+  </si>
+  <si>
+    <t>*HPS*</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt*</t>
+  </si>
+  <si>
+    <t>Util_Rep_Batt*</t>
+  </si>
+  <si>
+    <t>*nuc*</t>
+  </si>
+  <si>
     <t>ACT_UPS</t>
-  </si>
-  <si>
-    <t>*bio*</t>
-  </si>
-  <si>
-    <t>*coa*, *lig*</t>
-  </si>
-  <si>
-    <t>EA_OIL*, EP_OIL*</t>
-  </si>
-  <si>
-    <t>en_gas*, ea_gas*, ep_gas*</t>
-  </si>
-  <si>
-    <t>*HPS*</t>
-  </si>
-  <si>
-    <t>EN_STG_4hBatt*</t>
-  </si>
-  <si>
-    <t>Util_Rep_Batt*</t>
-  </si>
-  <si>
-    <t>*nuc*</t>
   </si>
   <si>
     <t>~TFM_AVA</t>
@@ -379,15 +382,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-    </font>
-    <font>
       <sz val="10.2"/>
       <color rgb="FF212529"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -564,12 +567,12 @@
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -1044,10 +1047,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1642,7 +1645,7 @@
       </c>
     </row>
     <row r="4" ht="16" spans="1:11">
-      <c r="A4" s="6"/>
+      <c r="A4" s="5"/>
     </row>
     <row r="7" spans="1:11">
       <c r="D7" t="s">
@@ -1714,14 +1717,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C5:K85"/>
+  <dimension ref="B5:K85"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="24.1818181818182" customWidth="1"/>
     <col min="4" max="4" width="14.0909090909091" customWidth="1"/>
+    <col min="5" max="5" width="10.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:6">
+    <row r="5" spans="2:6">
       <c r="C5" s="1" t="s">
         <v>23</v>
       </c>
@@ -1729,225 +1733,337 @@
       <c r="E5" s="2"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="3:6">
+    <row r="6" spans="2:6">
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="3:6">
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="5">
+      <c r="E7" s="4">
         <v>10</v>
       </c>
-      <c r="E7" s="5">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="3:6">
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
       <c r="C8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="4">
         <v>7</v>
       </c>
-      <c r="E8" s="5">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" ht="16" spans="3:6">
-      <c r="C9" s="6" t="s">
+    </row>
+    <row r="9" ht="16" spans="2:6">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="4">
         <v>10</v>
       </c>
-      <c r="E9" s="5">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="3:6">
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
       <c r="C10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="4">
         <v>8</v>
       </c>
-      <c r="E10" s="5">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" ht="16" spans="3:6">
-      <c r="C11" s="6" t="s">
+    </row>
+    <row r="11" ht="16" spans="2:6">
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="2">
         <v>1.5</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" ht="16" spans="3:6">
-      <c r="C12" s="6" t="s">
+    </row>
+    <row r="12" ht="16" spans="2:6">
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="2">
         <v>1.5</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="3:6">
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
       <c r="C13" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="3">
         <v>2</v>
       </c>
-      <c r="E13" s="3">
-        <v>1</v>
-      </c>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" spans="3:6">
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
       <c r="C14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="E14" s="3">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" ht="16" spans="3:6">
-      <c r="C15" s="7" t="s">
+    </row>
+    <row r="15" ht="16" spans="2:6">
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="3">
         <v>0</v>
       </c>
-      <c r="E15" s="3">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="3:6">
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
       <c r="C16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E16" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="4">
         <v>0</v>
       </c>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="3:6">
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="3:6">
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
+    <row r="18" spans="2:6">
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="3:6">
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
+    <row r="19" ht="16" spans="2:6">
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0</v>
+      </c>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="3:6">
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
+    <row r="20" spans="2:6">
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0</v>
+      </c>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="3:6">
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
+    <row r="21" ht="16" spans="2:6">
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="3:6">
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+    <row r="22" ht="16" spans="2:6">
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="E22" s="2"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="3:6">
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
+    <row r="23" spans="2:6">
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1</v>
+      </c>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="3:6">
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+    <row r="24" spans="2:6">
+      <c r="B24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1</v>
+      </c>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="3:6">
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
+    <row r="25" ht="16" spans="2:6">
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="3">
+        <v>1</v>
+      </c>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="3:6">
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+    <row r="26" spans="2:6">
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="3:6">
+    <row r="27" spans="2:6">
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="3:6">
+    <row r="28" spans="2:6">
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="3:6">
+    <row r="29" spans="2:6">
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="3:6">
+    <row r="30" spans="2:6">
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="3:6">
+    <row r="31" spans="2:6">
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="3:6">
+    <row r="32" spans="2:6">
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -1960,7 +2076,7 @@
     </row>
     <row r="54" spans="3:11">
       <c r="C54" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="3:11">
@@ -1975,31 +2091,31 @@
     </row>
     <row r="57" spans="3:11">
       <c r="C57" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>5</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K57" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="3:11">
@@ -2290,7 +2406,7 @@
     </row>
     <row r="84" spans="3:11">
       <c r="C84" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D84" s="9">
         <v>1</v>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -164,10 +164,33 @@
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
+    <author>xli9</author>
     <author>Xiao Li</author>
   </authors>
   <commentList>
-    <comment ref="C77" authorId="0">
+    <comment ref="E17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">
+different from CAN-TIMES</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C77" authorId="1">
       <text>
         <r>
           <rPr>
@@ -578,12 +601,18 @@
       <charset val="0"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -914,7 +943,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -938,16 +967,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -956,93 +985,93 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
@@ -1050,11 +1079,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1588,7 +1619,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="13">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -1702,10 +1733,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="10"/>
+      <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="10"/>
+      <c r="K11" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1883,8 +1914,8 @@
       <c r="D16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="2">
-        <v>35</v>
+      <c r="E16" s="7">
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="2:6">
@@ -1894,11 +1925,11 @@
       <c r="C17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="4">
-        <v>0</v>
+      <c r="E17" s="9">
+        <v>0.2</v>
       </c>
       <c r="F17" s="3"/>
     </row>
@@ -1909,11 +1940,11 @@
       <c r="C18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="4">
-        <v>0</v>
+      <c r="E18" s="9">
+        <v>0.2</v>
       </c>
       <c r="F18" s="3"/>
     </row>
@@ -1924,11 +1955,11 @@
       <c r="C19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="4">
-        <v>0</v>
+      <c r="E19" s="9">
+        <v>0.2</v>
       </c>
       <c r="F19" s="3"/>
     </row>
@@ -1939,11 +1970,11 @@
       <c r="C20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="4">
-        <v>0</v>
+      <c r="E20" s="9">
+        <v>0.5</v>
       </c>
       <c r="F20" s="3"/>
     </row>
@@ -1954,10 +1985,12 @@
       <c r="C21" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="2"/>
+      <c r="E21" s="9">
+        <v>0.8</v>
+      </c>
       <c r="F21" s="3"/>
     </row>
     <row r="22" ht="16" spans="2:6">
@@ -1967,7 +2000,7 @@
       <c r="C22" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E22" s="2"/>
@@ -1980,7 +2013,7 @@
       <c r="C23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E23" s="3">
@@ -1995,7 +2028,7 @@
       <c r="C24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E24" s="3">
@@ -2010,7 +2043,7 @@
       <c r="C25" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E25" s="3">
@@ -2025,11 +2058,11 @@
       <c r="C26" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E26" s="2">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="F26" s="3"/>
     </row>
@@ -2070,365 +2103,365 @@
       <c r="F32" s="3"/>
     </row>
     <row r="38" spans="3:5">
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="9" t="s">
+      <c r="C54" s="11" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9"/>
-      <c r="K56" s="9"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="9" t="s">
+      <c r="C57" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="D57" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="F57" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G57" s="9" t="s">
+      <c r="G57" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H57" s="9" t="s">
+      <c r="H57" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="I57" s="9" t="s">
+      <c r="I57" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="J57" s="9" t="s">
+      <c r="J57" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="K57" s="9" t="s">
+      <c r="K57" s="11" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9"/>
-      <c r="K58" s="9"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="11"/>
+      <c r="K58" s="11"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="9"/>
-      <c r="J59" s="9"/>
-      <c r="K59" s="9"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="11"/>
+      <c r="K59" s="11"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="9"/>
-      <c r="J60" s="9"/>
-      <c r="K60" s="9"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="11"/>
+      <c r="K60" s="11"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="9"/>
-      <c r="J61" s="9"/>
-      <c r="K61" s="9"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="11"/>
+      <c r="K61" s="11"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
-      <c r="I62" s="9"/>
-      <c r="J62" s="9"/>
-      <c r="K62" s="9"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="11"/>
+      <c r="J62" s="11"/>
+      <c r="K62" s="11"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
-      <c r="I63" s="9"/>
-      <c r="J63" s="9"/>
-      <c r="K63" s="9"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="11"/>
+      <c r="I63" s="11"/>
+      <c r="J63" s="11"/>
+      <c r="K63" s="11"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
-      <c r="I64" s="9"/>
-      <c r="J64" s="9"/>
-      <c r="K64" s="9"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="11"/>
+      <c r="J64" s="11"/>
+      <c r="K64" s="11"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-      <c r="I65" s="9"/>
-      <c r="J65" s="9"/>
-      <c r="K65" s="9"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="11"/>
+      <c r="K65" s="11"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
-      <c r="I66" s="9"/>
-      <c r="J66" s="9"/>
-      <c r="K66" s="9"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="11"/>
+      <c r="K66" s="11"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
-      <c r="I67" s="9"/>
-      <c r="J67" s="9"/>
-      <c r="K67" s="9"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="11"/>
+      <c r="J67" s="11"/>
+      <c r="K67" s="11"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
-      <c r="I68" s="9"/>
-      <c r="J68" s="9"/>
-      <c r="K68" s="9"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="11"/>
+      <c r="I68" s="11"/>
+      <c r="J68" s="11"/>
+      <c r="K68" s="11"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
-      <c r="I69" s="9"/>
-      <c r="J69" s="9"/>
-      <c r="K69" s="9"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
+      <c r="K69" s="11"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="9"/>
-      <c r="H70" s="9"/>
-      <c r="I70" s="9"/>
-      <c r="J70" s="9"/>
-      <c r="K70" s="9"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="11"/>
+      <c r="I70" s="11"/>
+      <c r="J70" s="11"/>
+      <c r="K70" s="11"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="9"/>
-      <c r="J71" s="9"/>
-      <c r="K71" s="9"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
+      <c r="K71" s="11"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="9"/>
-      <c r="J72" s="9"/>
-      <c r="K72" s="9"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="11"/>
+      <c r="K72" s="11"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="9"/>
-      <c r="J73" s="9"/>
-      <c r="K73" s="9"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="11"/>
+      <c r="K73" s="11"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="9"/>
-      <c r="J74" s="9"/>
-      <c r="K74" s="9"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11"/>
+      <c r="I74" s="11"/>
+      <c r="J74" s="11"/>
+      <c r="K74" s="11"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="9"/>
-      <c r="J75" s="9"/>
-      <c r="K75" s="9"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="11"/>
+      <c r="J75" s="11"/>
+      <c r="K75" s="11"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="9"/>
-      <c r="J76" s="9"/>
-      <c r="K76" s="9"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="11"/>
+      <c r="K76" s="11"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-      <c r="I77" s="9"/>
-      <c r="J77" s="9"/>
-      <c r="K77" s="9"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="11"/>
+      <c r="J77" s="11"/>
+      <c r="K77" s="11"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-      <c r="I78" s="9"/>
-      <c r="J78" s="9"/>
-      <c r="K78" s="9"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="11"/>
+      <c r="J78" s="11"/>
+      <c r="K78" s="11"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-      <c r="I79" s="9"/>
-      <c r="J79" s="9"/>
-      <c r="K79" s="9"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="11"/>
+      <c r="G79" s="11"/>
+      <c r="H79" s="11"/>
+      <c r="I79" s="11"/>
+      <c r="J79" s="11"/>
+      <c r="K79" s="11"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
-      <c r="I80" s="9"/>
-      <c r="J80" s="9"/>
-      <c r="K80" s="9"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="11"/>
+      <c r="J80" s="11"/>
+      <c r="K80" s="11"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
-      <c r="I81" s="9"/>
-      <c r="J81" s="9"/>
-      <c r="K81" s="9"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="11"/>
+      <c r="H81" s="11"/>
+      <c r="I81" s="11"/>
+      <c r="J81" s="11"/>
+      <c r="K81" s="11"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9"/>
-      <c r="I82" s="9"/>
-      <c r="J82" s="9"/>
-      <c r="K82" s="9"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
+      <c r="F82" s="11"/>
+      <c r="G82" s="11"/>
+      <c r="H82" s="11"/>
+      <c r="I82" s="11"/>
+      <c r="J82" s="11"/>
+      <c r="K82" s="11"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
-      <c r="F83" s="9"/>
-      <c r="G83" s="9"/>
-      <c r="H83" s="9"/>
-      <c r="I83" s="9"/>
-      <c r="J83" s="9"/>
-      <c r="K83" s="9"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11"/>
+      <c r="G83" s="11"/>
+      <c r="H83" s="11"/>
+      <c r="I83" s="11"/>
+      <c r="J83" s="11"/>
+      <c r="K83" s="11"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="9" t="s">
+      <c r="C84" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D84" s="9">
+      <c r="D84" s="11">
         <v>1</v>
       </c>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9"/>
-      <c r="I84" s="9"/>
-      <c r="J84" s="9"/>
-      <c r="K84" s="9"/>
+      <c r="E84" s="11"/>
+      <c r="F84" s="11"/>
+      <c r="G84" s="11"/>
+      <c r="H84" s="11"/>
+      <c r="I84" s="11"/>
+      <c r="J84" s="11"/>
+      <c r="K84" s="11"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="9"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="9"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9"/>
-      <c r="H85" s="9"/>
-      <c r="I85" s="9"/>
-      <c r="J85" s="9"/>
-      <c r="K85" s="9"/>
+      <c r="C85" s="11"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="11"/>
+      <c r="F85" s="11"/>
+      <c r="G85" s="11"/>
+      <c r="H85" s="11"/>
+      <c r="I85" s="11"/>
+      <c r="J85" s="11"/>
+      <c r="K85" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -217,7 +217,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="56">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -333,7 +333,13 @@
     <t>EA_OIL*, EP_OIL*</t>
   </si>
   <si>
+    <t>China</t>
+  </si>
+  <si>
     <t>en_gas*, ea_gas*, ep_gas*</t>
+  </si>
+  <si>
+    <t>CAP_BND</t>
   </si>
   <si>
     <t>*HPS*</t>
@@ -391,7 +397,7 @@
     <numFmt numFmtId="176" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -407,6 +413,12 @@
     <font>
       <sz val="10.2"/>
       <color rgb="FF212529"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF3974D2"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
@@ -579,17 +591,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
@@ -601,12 +613,18 @@
       <charset val="0"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -937,55 +955,52 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1000,92 +1015,99 @@
     <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1619,7 +1641,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="15">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -1733,10 +1755,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="12"/>
+      <c r="K10" s="14"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="12"/>
+      <c r="K11" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1748,7 +1770,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B5:K85"/>
+  <dimension ref="B5:N85"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="24.1818181818182" customWidth="1"/>
@@ -1756,7 +1778,7 @@
     <col min="5" max="5" width="10.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:6">
+    <row r="5" spans="2:14">
       <c r="C5" s="1" t="s">
         <v>23</v>
       </c>
@@ -1764,7 +1786,7 @@
       <c r="E5" s="2"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="2:14">
       <c r="B6" t="s">
         <v>33</v>
       </c>
@@ -1778,7 +1800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="2:14">
       <c r="B7" t="s">
         <v>17</v>
       </c>
@@ -1792,7 +1814,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:6">
+    <row r="8" spans="2:14">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -1805,8 +1827,13 @@
       <c r="E8" s="4">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" ht="16" spans="2:6">
+      <c r="K8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" ht="16" spans="2:14">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -1819,13 +1846,28 @@
       <c r="E9" s="4">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="2:6">
+      <c r="J9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" ht="32" spans="2:14">
       <c r="B10" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>35</v>
@@ -1833,8 +1875,20 @@
       <c r="E10" s="4">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" ht="16" spans="2:6">
+      <c r="K10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M10">
+        <v>50</v>
+      </c>
+      <c r="N10">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" ht="16" spans="2:14">
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -1848,7 +1902,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="12" ht="16" spans="2:6">
+    <row r="12" ht="16" spans="2:14">
       <c r="B12" t="s">
         <v>17</v>
       </c>
@@ -1862,12 +1916,12 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="13" spans="2:6">
+    <row r="13" spans="2:14">
       <c r="B13" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>35</v>
@@ -1876,12 +1930,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:6">
+    <row r="14" spans="2:14">
       <c r="B14" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>35</v>
@@ -1890,12 +1944,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="16" spans="2:6">
+    <row r="15" ht="16" spans="2:14">
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>41</v>
+      <c r="C15" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>35</v>
@@ -1904,17 +1958,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:6">
+    <row r="16" spans="2:14">
       <c r="B16" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="9">
         <v>12</v>
       </c>
     </row>
@@ -1925,10 +1979,10 @@
       <c r="C17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="9">
+      <c r="D17" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="11">
         <v>0.2</v>
       </c>
       <c r="F17" s="3"/>
@@ -1940,10 +1994,10 @@
       <c r="C18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="9">
+      <c r="D18" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="11">
         <v>0.2</v>
       </c>
       <c r="F18" s="3"/>
@@ -1955,10 +2009,10 @@
       <c r="C19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E19" s="9">
+      <c r="D19" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="11">
         <v>0.2</v>
       </c>
       <c r="F19" s="3"/>
@@ -1968,12 +2022,12 @@
         <v>17</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="9">
+        <v>39</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="11">
         <v>0.5</v>
       </c>
       <c r="F20" s="3"/>
@@ -1985,10 +2039,10 @@
       <c r="C21" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="9">
+      <c r="D21" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="11">
         <v>0.8</v>
       </c>
       <c r="F21" s="3"/>
@@ -2000,8 +2054,8 @@
       <c r="C22" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>43</v>
+      <c r="D22" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="3"/>
@@ -2011,10 +2065,10 @@
         <v>17</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="E23" s="3">
         <v>1</v>
@@ -2026,10 +2080,10 @@
         <v>17</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="E24" s="3">
         <v>1</v>
@@ -2040,11 +2094,11 @@
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="8" t="s">
+      <c r="C25" s="8" t="s">
         <v>43</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="E25" s="3">
         <v>1</v>
@@ -2056,10 +2110,10 @@
         <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="E26" s="2">
         <v>0.05</v>
@@ -2103,365 +2157,365 @@
       <c r="F32" s="3"/>
     </row>
     <row r="38" spans="3:5">
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="11" t="s">
-        <v>44</v>
+      <c r="C54" s="13" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11"/>
-      <c r="I56" s="11"/>
-      <c r="J56" s="11"/>
-      <c r="K56" s="11"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="K56" s="13"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D57" s="11" t="s">
+      <c r="C57" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D57" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F57" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G57" s="11" t="s">
+      <c r="E57" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="H57" s="11" t="s">
+      <c r="F57" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="I57" s="11" t="s">
+      <c r="G57" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="J57" s="11" t="s">
+      <c r="H57" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="K57" s="11" t="s">
+      <c r="I57" s="13" t="s">
         <v>52</v>
       </c>
+      <c r="J57" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="K57" s="13" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="11"/>
-      <c r="I58" s="11"/>
-      <c r="J58" s="11"/>
-      <c r="K58" s="11"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="K58" s="13"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="11"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="11"/>
-      <c r="I59" s="11"/>
-      <c r="J59" s="11"/>
-      <c r="K59" s="11"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="13"/>
+      <c r="K59" s="13"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="11"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
-      <c r="H60" s="11"/>
-      <c r="I60" s="11"/>
-      <c r="J60" s="11"/>
-      <c r="K60" s="11"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="11"/>
-      <c r="I61" s="11"/>
-      <c r="J61" s="11"/>
-      <c r="K61" s="11"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="11"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="11"/>
-      <c r="I62" s="11"/>
-      <c r="J62" s="11"/>
-      <c r="K62" s="11"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13"/>
+      <c r="K62" s="13"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="11"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
-      <c r="H63" s="11"/>
-      <c r="I63" s="11"/>
-      <c r="J63" s="11"/>
-      <c r="K63" s="11"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="13"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="13"/>
+      <c r="J63" s="13"/>
+      <c r="K63" s="13"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="11"/>
-      <c r="D64" s="11"/>
-      <c r="E64" s="11"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="11"/>
-      <c r="H64" s="11"/>
-      <c r="I64" s="11"/>
-      <c r="J64" s="11"/>
-      <c r="K64" s="11"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="13"/>
+      <c r="H64" s="13"/>
+      <c r="I64" s="13"/>
+      <c r="J64" s="13"/>
+      <c r="K64" s="13"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
-      <c r="H65" s="11"/>
-      <c r="I65" s="11"/>
-      <c r="J65" s="11"/>
-      <c r="K65" s="11"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="13"/>
+      <c r="K65" s="13"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="11"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="11"/>
-      <c r="H66" s="11"/>
-      <c r="I66" s="11"/>
-      <c r="J66" s="11"/>
-      <c r="K66" s="11"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="13"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="11"/>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="11"/>
-      <c r="I67" s="11"/>
-      <c r="J67" s="11"/>
-      <c r="K67" s="11"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13"/>
+      <c r="K67" s="13"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="11"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="11"/>
-      <c r="I68" s="11"/>
-      <c r="J68" s="11"/>
-      <c r="K68" s="11"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+      <c r="K68" s="13"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="11"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="11"/>
-      <c r="H69" s="11"/>
-      <c r="I69" s="11"/>
-      <c r="J69" s="11"/>
-      <c r="K69" s="11"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+      <c r="K69" s="13"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="11"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="11"/>
-      <c r="G70" s="11"/>
-      <c r="H70" s="11"/>
-      <c r="I70" s="11"/>
-      <c r="J70" s="11"/>
-      <c r="K70" s="11"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
+      <c r="J70" s="13"/>
+      <c r="K70" s="13"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="11"/>
-      <c r="H71" s="11"/>
-      <c r="I71" s="11"/>
-      <c r="J71" s="11"/>
-      <c r="K71" s="11"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="13"/>
+      <c r="J71" s="13"/>
+      <c r="K71" s="13"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="11"/>
-      <c r="I72" s="11"/>
-      <c r="J72" s="11"/>
-      <c r="K72" s="11"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="13"/>
+      <c r="J72" s="13"/>
+      <c r="K72" s="13"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="11"/>
-      <c r="I73" s="11"/>
-      <c r="J73" s="11"/>
-      <c r="K73" s="11"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="13"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="13"/>
+      <c r="K73" s="13"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="11"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="11"/>
-      <c r="H74" s="11"/>
-      <c r="I74" s="11"/>
-      <c r="J74" s="11"/>
-      <c r="K74" s="11"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="13"/>
+      <c r="J74" s="13"/>
+      <c r="K74" s="13"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="11"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="11"/>
-      <c r="H75" s="11"/>
-      <c r="I75" s="11"/>
-      <c r="J75" s="11"/>
-      <c r="K75" s="11"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
+      <c r="J75" s="13"/>
+      <c r="K75" s="13"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="11"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="11"/>
-      <c r="H76" s="11"/>
-      <c r="I76" s="11"/>
-      <c r="J76" s="11"/>
-      <c r="K76" s="11"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="13"/>
+      <c r="E76" s="13"/>
+      <c r="F76" s="13"/>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="13"/>
+      <c r="J76" s="13"/>
+      <c r="K76" s="13"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="11"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="11"/>
-      <c r="H77" s="11"/>
-      <c r="I77" s="11"/>
-      <c r="J77" s="11"/>
-      <c r="K77" s="11"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="13"/>
+      <c r="K77" s="13"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="11"/>
-      <c r="D78" s="11"/>
-      <c r="E78" s="11"/>
-      <c r="F78" s="11"/>
-      <c r="G78" s="11"/>
-      <c r="H78" s="11"/>
-      <c r="I78" s="11"/>
-      <c r="J78" s="11"/>
-      <c r="K78" s="11"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="13"/>
+      <c r="E78" s="13"/>
+      <c r="F78" s="13"/>
+      <c r="G78" s="13"/>
+      <c r="H78" s="13"/>
+      <c r="I78" s="13"/>
+      <c r="J78" s="13"/>
+      <c r="K78" s="13"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="11"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="11"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="11"/>
-      <c r="H79" s="11"/>
-      <c r="I79" s="11"/>
-      <c r="J79" s="11"/>
-      <c r="K79" s="11"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="13"/>
+      <c r="E79" s="13"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="13"/>
+      <c r="J79" s="13"/>
+      <c r="K79" s="13"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="11"/>
-      <c r="D80" s="11"/>
-      <c r="E80" s="11"/>
-      <c r="F80" s="11"/>
-      <c r="G80" s="11"/>
-      <c r="H80" s="11"/>
-      <c r="I80" s="11"/>
-      <c r="J80" s="11"/>
-      <c r="K80" s="11"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="13"/>
+      <c r="E80" s="13"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="13"/>
+      <c r="H80" s="13"/>
+      <c r="I80" s="13"/>
+      <c r="J80" s="13"/>
+      <c r="K80" s="13"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="11"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
-      <c r="G81" s="11"/>
-      <c r="H81" s="11"/>
-      <c r="I81" s="11"/>
-      <c r="J81" s="11"/>
-      <c r="K81" s="11"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="13"/>
+      <c r="E81" s="13"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="13"/>
+      <c r="H81" s="13"/>
+      <c r="I81" s="13"/>
+      <c r="J81" s="13"/>
+      <c r="K81" s="13"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="11"/>
-      <c r="D82" s="11"/>
-      <c r="E82" s="11"/>
-      <c r="F82" s="11"/>
-      <c r="G82" s="11"/>
-      <c r="H82" s="11"/>
-      <c r="I82" s="11"/>
-      <c r="J82" s="11"/>
-      <c r="K82" s="11"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="13"/>
+      <c r="H82" s="13"/>
+      <c r="I82" s="13"/>
+      <c r="J82" s="13"/>
+      <c r="K82" s="13"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="11"/>
-      <c r="D83" s="11"/>
-      <c r="E83" s="11"/>
-      <c r="F83" s="11"/>
-      <c r="G83" s="11"/>
-      <c r="H83" s="11"/>
-      <c r="I83" s="11"/>
-      <c r="J83" s="11"/>
-      <c r="K83" s="11"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="13"/>
+      <c r="E83" s="13"/>
+      <c r="F83" s="13"/>
+      <c r="G83" s="13"/>
+      <c r="H83" s="13"/>
+      <c r="I83" s="13"/>
+      <c r="J83" s="13"/>
+      <c r="K83" s="13"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D84" s="11">
+      <c r="C84" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D84" s="13">
         <v>1</v>
       </c>
-      <c r="E84" s="11"/>
-      <c r="F84" s="11"/>
-      <c r="G84" s="11"/>
-      <c r="H84" s="11"/>
-      <c r="I84" s="11"/>
-      <c r="J84" s="11"/>
-      <c r="K84" s="11"/>
+      <c r="E84" s="13"/>
+      <c r="F84" s="13"/>
+      <c r="G84" s="13"/>
+      <c r="H84" s="13"/>
+      <c r="I84" s="13"/>
+      <c r="J84" s="13"/>
+      <c r="K84" s="13"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="11"/>
-      <c r="D85" s="11"/>
-      <c r="E85" s="11"/>
-      <c r="F85" s="11"/>
-      <c r="G85" s="11"/>
-      <c r="H85" s="11"/>
-      <c r="I85" s="11"/>
-      <c r="J85" s="11"/>
-      <c r="K85" s="11"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="13"/>
+      <c r="E85" s="13"/>
+      <c r="F85" s="13"/>
+      <c r="G85" s="13"/>
+      <c r="H85" s="13"/>
+      <c r="I85" s="13"/>
+      <c r="J85" s="13"/>
+      <c r="K85" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -168,6 +168,28 @@
     <author>Xiao Li</author>
   </authors>
   <commentList>
+    <comment ref="K6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">
+Should not because then system will rely on HPS without battery expansion</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E17" authorId="0">
       <text>
         <r>
@@ -591,17 +613,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
@@ -622,6 +644,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -629,12 +657,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1089,24 +1111,25 @@
     <xf numFmtId="0" fontId="26" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="53">
@@ -1641,7 +1664,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="16">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -1698,7 +1721,7 @@
       </c>
     </row>
     <row r="4" ht="16" spans="1:11">
-      <c r="A4" s="5"/>
+      <c r="A4" s="6"/>
     </row>
     <row r="7" spans="1:11">
       <c r="D7" t="s">
@@ -1755,10 +1778,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="14"/>
+      <c r="K10" s="15"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="14"/>
+      <c r="K11" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1799,6 +1822,9 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
+      <c r="K6" s="4" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="2:14">
       <c r="B7" t="s">
@@ -1810,7 +1836,7 @@
       <c r="D7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="5">
         <v>10</v>
       </c>
     </row>
@@ -1824,11 +1850,8 @@
       <c r="D8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="5">
         <v>7</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>0</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -1837,13 +1860,13 @@
       <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="5">
         <v>10</v>
       </c>
       <c r="J9" t="s">
@@ -1872,13 +1895,13 @@
       <c r="D10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="5">
         <v>8</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="8" t="s">
         <v>40</v>
       </c>
       <c r="M10">
@@ -1892,7 +1915,7 @@
       <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="2" t="s">
@@ -1906,7 +1929,7 @@
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D12" s="2" t="s">
@@ -1948,7 +1971,7 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="9" t="s">
         <v>43</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -1968,7 +1991,7 @@
       <c r="D16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="10">
         <v>12</v>
       </c>
     </row>
@@ -1979,10 +2002,10 @@
       <c r="C17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="12">
         <v>0.2</v>
       </c>
       <c r="F17" s="3"/>
@@ -1994,10 +2017,10 @@
       <c r="C18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="12">
         <v>0.2</v>
       </c>
       <c r="F18" s="3"/>
@@ -2006,13 +2029,13 @@
       <c r="B19" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="12">
         <v>0.2</v>
       </c>
       <c r="F19" s="3"/>
@@ -2024,10 +2047,10 @@
       <c r="C20" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="12">
         <v>0.5</v>
       </c>
       <c r="F20" s="3"/>
@@ -2036,13 +2059,13 @@
       <c r="B21" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="12">
         <v>0.8</v>
       </c>
       <c r="F21" s="3"/>
@@ -2051,10 +2074,10 @@
       <c r="B22" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="11" t="s">
         <v>45</v>
       </c>
       <c r="E22" s="2"/>
@@ -2067,7 +2090,7 @@
       <c r="C23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="11" t="s">
         <v>45</v>
       </c>
       <c r="E23" s="3">
@@ -2082,7 +2105,7 @@
       <c r="C24" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>45</v>
       </c>
       <c r="E24" s="3">
@@ -2094,10 +2117,10 @@
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="11" t="s">
         <v>45</v>
       </c>
       <c r="E25" s="3">
@@ -2112,7 +2135,7 @@
       <c r="C26" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="11" t="s">
         <v>45</v>
       </c>
       <c r="E26" s="2">
@@ -2157,365 +2180,365 @@
       <c r="F32" s="3"/>
     </row>
     <row r="38" spans="3:5">
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="14" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="13"/>
-      <c r="K56" s="13"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="14"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="13" t="s">
+      <c r="C57" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D57" s="13" t="s">
+      <c r="D57" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="13" t="s">
+      <c r="E57" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="F57" s="13" t="s">
+      <c r="F57" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="G57" s="13" t="s">
+      <c r="G57" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="H57" s="13" t="s">
+      <c r="H57" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="I57" s="13" t="s">
+      <c r="I57" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="J57" s="13" t="s">
+      <c r="J57" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="K57" s="13" t="s">
+      <c r="K57" s="14" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="13"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
-      <c r="K58" s="13"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="14"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="13"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="13"/>
-      <c r="K59" s="13"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="13"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="14"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="13"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="13"/>
-      <c r="J61" s="13"/>
-      <c r="K61" s="13"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="14"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="13"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="13"/>
-      <c r="J62" s="13"/>
-      <c r="K62" s="13"/>
+      <c r="C62" s="14"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="14"/>
+      <c r="F62" s="14"/>
+      <c r="G62" s="14"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="14"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="13"/>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="13"/>
-      <c r="H63" s="13"/>
-      <c r="I63" s="13"/>
-      <c r="J63" s="13"/>
-      <c r="K63" s="13"/>
+      <c r="C63" s="14"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="14"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="13"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="13"/>
-      <c r="J64" s="13"/>
-      <c r="K64" s="13"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="14"/>
+      <c r="K64" s="14"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="13"/>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="13"/>
-      <c r="J65" s="13"/>
-      <c r="K65" s="13"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="14"/>
+      <c r="K65" s="14"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="13"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="13"/>
-      <c r="J66" s="13"/>
-      <c r="K66" s="13"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="14"/>
+      <c r="K66" s="14"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="13"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="13"/>
-      <c r="J67" s="13"/>
-      <c r="K67" s="13"/>
+      <c r="C67" s="14"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
+      <c r="H67" s="14"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="14"/>
+      <c r="K67" s="14"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="13"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-      <c r="K68" s="13"/>
+      <c r="C68" s="14"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="14"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="13"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
-      <c r="K69" s="13"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+      <c r="K69" s="14"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="13"/>
-      <c r="J70" s="13"/>
-      <c r="K70" s="13"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+      <c r="K70" s="14"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="13"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
-      <c r="J71" s="13"/>
-      <c r="K71" s="13"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="14"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="13"/>
-      <c r="K72" s="13"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+      <c r="K72" s="14"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="13"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-      <c r="J73" s="13"/>
-      <c r="K73" s="13"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+      <c r="K73" s="14"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
-      <c r="J74" s="13"/>
-      <c r="K74" s="13"/>
+      <c r="C74" s="14"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+      <c r="K74" s="14"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="13"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="13"/>
-      <c r="J75" s="13"/>
-      <c r="K75" s="13"/>
+      <c r="C75" s="14"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="14"/>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+      <c r="K75" s="14"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="13"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="13"/>
-      <c r="J76" s="13"/>
-      <c r="K76" s="13"/>
+      <c r="C76" s="14"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="14"/>
+      <c r="H76" s="14"/>
+      <c r="I76" s="14"/>
+      <c r="J76" s="14"/>
+      <c r="K76" s="14"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="13"/>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="13"/>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13"/>
-      <c r="I77" s="13"/>
-      <c r="J77" s="13"/>
-      <c r="K77" s="13"/>
+      <c r="C77" s="14"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="14"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="14"/>
+      <c r="K77" s="14"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="13"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="13"/>
-      <c r="J78" s="13"/>
-      <c r="K78" s="13"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="14"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="14"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
+      <c r="K78" s="14"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="13"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
-      <c r="I79" s="13"/>
-      <c r="J79" s="13"/>
-      <c r="K79" s="13"/>
+      <c r="C79" s="14"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="14"/>
+      <c r="G79" s="14"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
+      <c r="K79" s="14"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="13"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
-      <c r="F80" s="13"/>
-      <c r="G80" s="13"/>
-      <c r="H80" s="13"/>
-      <c r="I80" s="13"/>
-      <c r="J80" s="13"/>
-      <c r="K80" s="13"/>
+      <c r="C80" s="14"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="14"/>
+      <c r="F80" s="14"/>
+      <c r="G80" s="14"/>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="14"/>
+      <c r="K80" s="14"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="13"/>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
-      <c r="G81" s="13"/>
-      <c r="H81" s="13"/>
-      <c r="I81" s="13"/>
-      <c r="J81" s="13"/>
-      <c r="K81" s="13"/>
+      <c r="C81" s="14"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="14"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="14"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14"/>
+      <c r="K81" s="14"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="13"/>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13"/>
-      <c r="F82" s="13"/>
-      <c r="G82" s="13"/>
-      <c r="H82" s="13"/>
-      <c r="I82" s="13"/>
-      <c r="J82" s="13"/>
-      <c r="K82" s="13"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="14"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14"/>
+      <c r="K82" s="14"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="13"/>
-      <c r="D83" s="13"/>
-      <c r="E83" s="13"/>
-      <c r="F83" s="13"/>
-      <c r="G83" s="13"/>
-      <c r="H83" s="13"/>
-      <c r="I83" s="13"/>
-      <c r="J83" s="13"/>
-      <c r="K83" s="13"/>
+      <c r="C83" s="14"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="14"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="14"/>
+      <c r="K83" s="14"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="13" t="s">
+      <c r="C84" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D84" s="13">
+      <c r="D84" s="14">
         <v>1</v>
       </c>
-      <c r="E84" s="13"/>
-      <c r="F84" s="13"/>
-      <c r="G84" s="13"/>
-      <c r="H84" s="13"/>
-      <c r="I84" s="13"/>
-      <c r="J84" s="13"/>
-      <c r="K84" s="13"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
+      <c r="K84" s="14"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="13"/>
-      <c r="D85" s="13"/>
-      <c r="E85" s="13"/>
-      <c r="F85" s="13"/>
-      <c r="G85" s="13"/>
-      <c r="H85" s="13"/>
-      <c r="I85" s="13"/>
-      <c r="J85" s="13"/>
-      <c r="K85" s="13"/>
+      <c r="C85" s="14"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="14"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14"/>
+      <c r="K85" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
